--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -45,21 +45,21 @@
     <t xml:space="preserve">Huasco</t>
   </si>
   <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Vallenar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chañaral</t>
+    <t xml:space="preserve">Diego de Almagro</t>
   </si>
   <si>
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1413</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>599</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>494</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>343</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +564,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3301</v>
+        <v>3201</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>56</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -581,13 +581,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3201</v>
+        <v>3302</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-259</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3103</v>
+        <v>3202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1002</v>
+        <v>-465</v>
       </c>
     </row>
     <row r="9">
@@ -615,13 +615,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3202</v>
+        <v>3103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1260</v>
+        <v>-501</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-4436</v>
+        <v>-1070</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-05 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
